--- a/hasil_pengujian/LAPORAN_PENGUJIAN_INTERVU.xlsx
+++ b/hasil_pengujian/LAPORAN_PENGUJIAN_INTERVU.xlsx
@@ -1,26 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13341AE-F096-4E12-BA99-3FD8383CDF09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="120" yWindow="570" windowWidth="20490" windowHeight="10515" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="1. Ringkasan Eksekutif" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="2. Environment &amp; Setup" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="3. Alur E2E Lengkap" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="4. Unit Tests" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="5. API &amp; Integration Tests" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="6. E2E Playwright Tests" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="7. Temuan &amp; Rekomendasi" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="8. Detail Skor Evaluasi" state="visible" r:id="rId11"/>
+    <sheet name="1. Ringkasan Eksekutif" sheetId="1" r:id="rId1"/>
+    <sheet name="2. Environment &amp; Setup" sheetId="2" r:id="rId2"/>
+    <sheet name="3. Alur E2E Lengkap" sheetId="3" r:id="rId3"/>
+    <sheet name="4. Unit Tests" sheetId="4" r:id="rId4"/>
+    <sheet name="5. API &amp; Integration Tests" sheetId="5" r:id="rId5"/>
+    <sheet name="6. E2E Playwright Tests" sheetId="6" r:id="rId6"/>
+    <sheet name="7. Temuan &amp; Rekomendasi" sheetId="7" r:id="rId7"/>
+    <sheet name="8. Detail Skor Evaluasi" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="615">
   <si>
-    <t xml:space="preserve">LAPORAN PENGUJIAN SISTEM INTERV-U
+    <t>LAPORAN PENGUJIAN SISTEM INTERV-U
 AI Interview Simulator — Laporan Lengkap Berbasis Data Nyata</t>
   </si>
   <si>
@@ -54,7 +71,7 @@
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit &amp; Algorithmic Testing
+    <t>Unit &amp; Algorithmic Testing
 (Logika algoritma JS murni)</t>
   </si>
   <si>
@@ -67,14 +84,14 @@
     <t>2</t>
   </si>
   <si>
-    <t xml:space="preserve">Black-Box API &amp; Integration Testing
+    <t>Black-Box API &amp; Integration Testing
 (Semua endpoint REST API)</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t xml:space="preserve">End-to-End Testing Playwright
+    <t>End-to-End Testing Playwright
 (Browser Headless Chromium)</t>
   </si>
   <si>
@@ -471,7 +488,7 @@
     <t>Landing page animasi orbital, tombol "Mulai Sekarang", ilustrasi AI.</t>
   </si>
   <si>
-    <t xml:space="preserve">components/Landing.tsx
+    <t>components/Landing.tsx
 app/page.tsx
 contexts/AuthContext.tsx</t>
   </si>
@@ -494,12 +511,12 @@
     <t>Tombol Google OAuth. Redirect ke / setelah login sukses.</t>
   </si>
   <si>
-    <t xml:space="preserve">app/login/page.tsx
+    <t>app/login/page.tsx
 contexts/AuthContext.tsx
 lib/firebase.ts</t>
   </si>
   <si>
-    <t xml:space="preserve">Firebase Auth
+    <t>Firebase Auth
 (Google OAuth)</t>
   </si>
   <si>
@@ -524,11 +541,11 @@
     <t>State cvData &amp; jdData terisi dari response API extract.</t>
   </si>
   <si>
-    <t xml:space="preserve">components/Onboarding.tsx
+    <t>components/Onboarding.tsx
 app/api/extract/route.ts</t>
   </si>
   <si>
-    <t xml:space="preserve">POST /api/extract
+    <t>POST /api/extract
 (type: cv)
 POST /api/extract
 (type: jd)</t>
@@ -552,7 +569,7 @@
     <t>JSON: {profile, experience, education, skills[], certifications[]}</t>
   </si>
   <si>
-    <t xml:space="preserve">app/api/extract/route.ts
+    <t>app/api/extract/route.ts
 Gemini API (gemini-2.0-flash)</t>
   </si>
   <si>
@@ -577,7 +594,7 @@
     <t>JSON: {role, company, requirements[], target_competencies:[{code, name, importance, weight}]}</t>
   </si>
   <si>
-    <t xml:space="preserve">app/api/extract/route.ts
+    <t>app/api/extract/route.ts
 contexts/pemetaan-kompetensi-it.md
 Gemini API</t>
   </si>
@@ -597,7 +614,7 @@
     <t>JSON: {match_score:65, matched_skills:[...12 items], gap_skills:[...], focus_areas:[...5 items], summary}</t>
   </si>
   <si>
-    <t xml:space="preserve">app/api/cross-match/route.ts
+    <t>app/api/cross-match/route.ts
 Gemini API</t>
   </si>
   <si>
@@ -616,7 +633,7 @@
     <t>State interviewMode terpilih. Transisi ke fase interview.</t>
   </si>
   <si>
-    <t xml:space="preserve">components/InterviewSetup.tsx
+    <t>components/InterviewSetup.tsx
 app/page.tsx</t>
   </si>
   <si>
@@ -638,14 +655,14 @@
     <t>JSON: {token: "&lt;ephemeral_token_76chars&gt;"}</t>
   </si>
   <si>
-    <t xml:space="preserve">app/api/live-token/route.ts
+    <t>app/api/live-token/route.ts
 Gemini Live API (v1beta)</t>
   </si>
   <si>
     <t>Google Gemini Live API</t>
   </si>
   <si>
-    <t xml:space="preserve">Diakses dari client-side
+    <t>Diakses dari client-side
 (token untuk WS)</t>
   </si>
   <si>
@@ -664,7 +681,7 @@
     <t>Koneksi WebSocket terbuka. AI siap menyapa kandidat.</t>
   </si>
   <si>
-    <t xml:space="preserve">components/LiveInterview.tsx
+    <t>components/LiveInterview.tsx
 lib/audio-manager.ts
 Gemini Live API WebSocket</t>
   </si>
@@ -693,7 +710,7 @@
     <t>Audio user terkirim ke Gemini Live AI untuk diproses.</t>
   </si>
   <si>
-    <t xml:space="preserve">lib/audio-manager.ts
+    <t>lib/audio-manager.ts
 components/LiveInterview.tsx</t>
   </si>
   <si>
@@ -715,7 +732,7 @@
     <t>Suara AI "Siti Rahayu" terdengar di speaker. Latency diukur.</t>
   </si>
   <si>
-    <t xml:space="preserve">components/LiveInterview.tsx
+    <t>components/LiveInterview.tsx
 lib/audio-manager.ts</t>
   </si>
   <si>
@@ -737,7 +754,7 @@
     <t>Transkrip terupdate real-time. Progress bar 1/7, 2/7, ... 7/7.</t>
   </si>
   <si>
-    <t xml:space="preserve">components/LiveInterview.tsx
+    <t>components/LiveInterview.tsx
 lib/evaluate.ts (analyzeFiller)</t>
   </si>
   <si>
@@ -759,7 +776,7 @@
     <t>Sesi berakhir. History transkrip diteruskan ke evaluasi.</t>
   </si>
   <si>
-    <t xml:space="preserve">components/LiveInterview.tsx
+    <t>components/LiveInterview.tsx
 app/page.tsx</t>
   </si>
   <si>
@@ -778,7 +795,7 @@
     <t>JSON: {qa_analysis:[7 items], competency_scores, overall_score:92, verdict, candidate_archetype:{type, label, description}, filler_analysis, recommendation}</t>
   </si>
   <si>
-    <t xml:space="preserve">app/api/evaluate/route.ts
+    <t>app/api/evaluate/route.ts
 lib/evaluate.ts
 Gemini API (gemini-2.5-flash)</t>
   </si>
@@ -798,7 +815,7 @@
     <t>Dasbor evaluasi lengkap ter-render. Data Gambar 5 skripsi berasal dari halaman ini.</t>
   </si>
   <si>
-    <t xml:space="preserve">components/InterviewEvaluation.tsx
+    <t>components/InterviewEvaluation.tsx
 app/page.tsx</t>
   </si>
   <si>
@@ -820,7 +837,7 @@
     <t>Sesi tersimpan di Firebase Firestore. Muncul di halaman /history.</t>
   </si>
   <si>
-    <t xml:space="preserve">lib/session-store.ts
+    <t>lib/session-store.ts
 Firebase Firestore
 lib/firebase.ts</t>
   </si>
@@ -846,7 +863,7 @@
     <t>JSON: {text: "&lt;coaching_response&gt;"} — respons 1.151 chars rata-rata</t>
   </si>
   <si>
-    <t xml:space="preserve">app/api/coaching/route.ts
+    <t>app/api/coaching/route.ts
 Gemini API (gemini-2.5-flash)</t>
   </si>
   <si>
@@ -868,7 +885,7 @@
     <t>JSON: {audioData: "&lt;base64_333504chars&gt;", mimeType: "audio/L16;codec=pcm;rate=24000"}</t>
   </si>
   <si>
-    <t xml:space="preserve">app/api/coaching/route.ts
+    <t>app/api/coaching/route.ts
 Gemini TTS API</t>
   </si>
   <si>
@@ -890,7 +907,7 @@
     <t>JSON: {is_better:true, rating:8, star:{score:3/4,...}, concise:{...}, improvement_note:"..."}</t>
   </si>
   <si>
-    <t xml:space="preserve">app/api/coaching/route.ts
+    <t>app/api/coaching/route.ts
 Gemini API</t>
   </si>
   <si>
@@ -924,13 +941,13 @@
     <t>Daftar semua sesi wawancara tersimpan terrender. User bisa buka detail atau hapus.</t>
   </si>
   <si>
-    <t xml:space="preserve">app/history/page.tsx
+    <t>app/history/page.tsx
 lib/session-store.ts
 components/InterviewEvaluation.tsx
 Firebase Firestore</t>
   </si>
   <si>
-    <t xml:space="preserve">Firebase Firestore
+    <t>Firebase Firestore
 (getUserSessions)</t>
   </si>
   <si>
@@ -952,7 +969,7 @@
     <t>Evaluasi sesi lama ter-render ulang identik dengan hasil evaluasi segar.</t>
   </si>
   <si>
-    <t xml:space="preserve">app/history/page.tsx
+    <t>app/history/page.tsx
 components/InterviewEvaluation.tsx</t>
   </si>
   <si>
@@ -977,7 +994,7 @@
     <t>Redirect ke /login jika belum auth. Lanjutkan jika sudah auth.</t>
   </si>
   <si>
-    <t xml:space="preserve">middleware.ts
+    <t>middleware.ts
 Firebase Auth</t>
   </si>
   <si>
@@ -1002,15 +1019,15 @@
     <t>User ter-logout. Kembali ke halaman login.</t>
   </si>
   <si>
-    <t xml:space="preserve">contexts/AuthContext.tsx
+    <t>contexts/AuthContext.tsx
 app/page.tsx</t>
   </si>
   <si>
-    <t xml:space="preserve">Firebase Auth
+    <t>Firebase Auth
 (signOut)</t>
   </si>
   <si>
-    <t xml:space="preserve">LAPISAN 1 — UNIT &amp; ALGORITHMIC TESTING
+    <t>LAPISAN 1 — UNIT &amp; ALGORITHMIC TESTING
 Script: hasil_pengujian/scripts/test_unit_algorithms.mjs  |  Waktu: &lt; 1 detik  |  Tanpa API Key / Network</t>
   </si>
   <si>
@@ -1038,7 +1055,7 @@
     <t>Filler Words — Level Clean</t>
   </si>
   <si>
-    <t xml:space="preserve">analyzeFiller()
+    <t>analyzeFiller()
 lib/evaluate.ts</t>
   </si>
   <si>
@@ -1048,7 +1065,7 @@
     <t>total: 0, level: "clean"</t>
   </si>
   <si>
-    <t xml:space="preserve">total: 0
+    <t>total: 0
 level: "clean"</t>
   </si>
   <si>
@@ -1064,7 +1081,7 @@
     <t>total: 2, level: "minimal"</t>
   </si>
   <si>
-    <t xml:space="preserve">total: 2
+    <t>total: 2
 level: "minimal"</t>
   </si>
   <si>
@@ -1080,7 +1097,7 @@
     <t>total: 4, level: "moderate"</t>
   </si>
   <si>
-    <t xml:space="preserve">total: 4
+    <t>total: 4
 level: "moderate"</t>
   </si>
   <si>
@@ -1099,7 +1116,7 @@
     <t>total: 9, level: "heavy"</t>
   </si>
   <si>
-    <t xml:space="preserve">total: 9
+    <t>total: 9
 level: "heavy"</t>
   </si>
   <si>
@@ -1118,7 +1135,7 @@
     <t>total: 0 — tidak ada false positive</t>
   </si>
   <si>
-    <t xml:space="preserve">total: 0
+    <t>total: 0
 Kata "teh" dan "manual" TIDAK memicu deteksi</t>
   </si>
   <si>
@@ -1137,7 +1154,7 @@
     <t>total: 3 (EH, HMM, KAYAK terdeteksi)</t>
   </si>
   <si>
-    <t xml:space="preserve">total: 3
+    <t>total: 3
 Semua kapital terdeteksi</t>
   </si>
   <si>
@@ -1150,18 +1167,18 @@
     <t>Audio WAV — Header RIFF &amp; WAVE</t>
   </si>
   <si>
-    <t xml:space="preserve">createWavHeader()
+    <t>createWavHeader()
 lib/audio-manager.ts</t>
   </si>
   <si>
     <t>Generate WAV header untuk audio PCM 24000Hz, 1 channel, 16-bit, 48000 data bytes</t>
   </si>
   <si>
-    <t xml:space="preserve">Bytes 0-4: "RIFF"
+    <t>Bytes 0-4: "RIFF"
 Bytes 8-12: "WAVE"</t>
   </si>
   <si>
-    <t xml:space="preserve">Header 0-4: "RIFF"
+    <t>Header 0-4: "RIFF"
 Header 8-12: "WAVE"</t>
   </si>
   <si>
@@ -1177,13 +1194,13 @@
     <t>Verifikasi field spesifik dalam WAV header: FormatTag, NumChannels, SampleRate, BitDepth</t>
   </si>
   <si>
-    <t xml:space="preserve">FormatTag: 1 (PCM)
+    <t>FormatTag: 1 (PCM)
 Channels: 1 (mono)
 SampleRate: 24000 Hz
 BitDepth: 16 bit</t>
   </si>
   <si>
-    <t xml:space="preserve">FormatTag: 1 ✓
+    <t>FormatTag: 1 ✓
 Channels: 1 ✓
 SampleRate: 24000 ✓
 BitDepth: 16 ✓</t>
@@ -1198,11 +1215,11 @@
     <t>JSON Field Extraction Helper</t>
   </si>
   <si>
-    <t xml:space="preserve">getField()
+    <t>getField()
 app/api/extract/route.ts</t>
   </si>
   <si>
-    <t xml:space="preserve">JSON string: {"jobTitle": "Frontend Developer", ...}
+    <t>JSON string: {"jobTitle": "Frontend Developer", ...}
 Key: "jobTitle"</t>
   </si>
   <si>
@@ -1218,18 +1235,18 @@
     <t>JSON Field Extraction Empty Fallback</t>
   </si>
   <si>
-    <t xml:space="preserve">JSON dengan key tidak ada
+    <t>JSON dengan key tidak ada
 Key: "nonExistentKey"</t>
   </si>
   <si>
     <t>"" (string kosong, bukan null/undefined/error)</t>
   </si>
   <si>
-    <t xml:space="preserve">"" (string kosong)
+    <t>"" (string kosong)
 Tidak throw error</t>
   </si>
   <si>
-    <t xml:space="preserve">LAPISAN 2 — BLACK-BOX API &amp; INTEGRATION TESTING
+    <t>LAPISAN 2 — BLACK-BOX API &amp; INTEGRATION TESTING
 Script: hasil_pengujian/scripts/test_api_endpoints.mjs  |  Data Uji Riil: CV_Avit_Febriansyah.pdf + loker.jpeg</t>
   </si>
   <si>
@@ -1251,7 +1268,7 @@
     <t>TC-API-01</t>
   </si>
   <si>
-    <t xml:space="preserve">GET
+    <t>GET
 /api/live-token</t>
   </si>
   <si>
@@ -1261,11 +1278,11 @@
     <t>GET (no body)</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200
+    <t>HTTP 200
 JSON: {token: string (length &gt; 0)}</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200 ✓
+    <t>HTTP 200 ✓
 token: 76 chars
 Format: string valid</t>
   </si>
@@ -1273,23 +1290,23 @@
     <t>TC-API-02</t>
   </si>
   <si>
-    <t xml:space="preserve">POST
+    <t>POST
 /api/extract
 (type: cv)</t>
   </si>
   <si>
-    <t xml:space="preserve">Positif: Ekstraksi CV PDF asli
+    <t>Positif: Ekstraksi CV PDF asli
 (CV_Avit_Febriansyah.pdf)</t>
   </si>
   <si>
     <t>{type:"cv", input:{file:{base64:&lt;pdf_base64&gt;, mimeType:"application/pdf"}}}</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200
+    <t>HTTP 200
 JSON: {profile:{name,...}, experience:[...], skills:[...], education:[...]}</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200 ✓
+    <t>HTTP 200 ✓
 Nama: AVIT FEBRIANSYAH
 Skills: 49 item
 Pengalaman: 2 entri
@@ -1299,23 +1316,23 @@
     <t>TC-API-03</t>
   </si>
   <si>
-    <t xml:space="preserve">POST
+    <t>POST
 /api/extract
 (type: jd)</t>
   </si>
   <si>
-    <t xml:space="preserve">Positif: Ekstraksi JD gambar asli
+    <t>Positif: Ekstraksi JD gambar asli
 (loker.jpeg) → Spencer &amp; Spencer</t>
   </si>
   <si>
     <t>{type:"jd", input:{file:{base64:&lt;jpeg_base64&gt;, mimeType:"image/jpeg"}}}</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200
+    <t>HTTP 200
 JSON: {role, company, requirements[], target_competencies:[{code,name,importance,weight}]}</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200 ✓
+    <t>HTTP 200 ✓
 Role: Full Stack Developer
 5 kompetensi Spencer:
 EXP, AT, CO, CT, ACH</t>
@@ -1324,24 +1341,24 @@
     <t>TC-API-04</t>
   </si>
   <si>
-    <t xml:space="preserve">POST
+    <t>POST
 /api/extract
 (Negatif)</t>
   </si>
   <si>
-    <t xml:space="preserve">Negatif: Input file kosong
+    <t>Negatif: Input file kosong
 (graceful handling)</t>
   </si>
   <si>
     <t>{type:"cv", input:{}}</t>
   </si>
   <si>
-    <t xml:space="preserve">Server tidak crash
+    <t>Server tidak crash
 HTTP 200 atau 400
 JSON terstruktur (bukan HTML error)</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200 ✓
+    <t>HTTP 200 ✓
 Server tidak crash
 Returns empty schema
 (Catatan: idealnya HTTP 400)</t>
@@ -1353,7 +1370,7 @@
     <t>TC-API-05</t>
   </si>
   <si>
-    <t xml:space="preserve">POST
+    <t>POST
 /api/cross-match</t>
   </si>
   <si>
@@ -1363,11 +1380,11 @@
     <t>{cvText: "&lt;hasil_extract_cv&gt;", jdText: "&lt;hasil_extract_jd&gt;"}</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200
+    <t>HTTP 200
 JSON: {match_score:number, matched_skills:[], gap_skills:[], focus_areas:[], summary}</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200 ✓
+    <t>HTTP 200 ✓
 match_score: 65/100
 matched_skills: 12 item
 focus_areas: 5 area
@@ -1377,22 +1394,22 @@
     <t>TC-API-06</t>
   </si>
   <si>
-    <t xml:space="preserve">POST
+    <t>POST
 /api/evaluate</t>
   </si>
   <si>
-    <t xml:space="preserve">Positif: LLM-as-a-Judge evaluasi
+    <t>Positif: LLM-as-a-Judge evaluasi
 transkrip 7 pertanyaan BEI</t>
   </si>
   <si>
     <t>{history:"&lt;7_QA_transcript&gt;", cvText, jdText, crossMatchData}</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200
+    <t>HTTP 200
 JSON: {qa_analysis:[...], competency_scores, overall_score, verdict, candidate_archetype, filler_analysis}</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200 ✓
+    <t>HTTP 200 ✓
 overall_score: 92/100
 Archetype: "The Star Performer (Jawara Sejati)"
 Avg STAR: 4.0/4
@@ -1403,7 +1420,7 @@
     <t>TC-API-07</t>
   </si>
   <si>
-    <t xml:space="preserve">POST
+    <t>POST
 /api/coaching
 (action: chat)</t>
   </si>
@@ -1414,12 +1431,12 @@
     <t>{action:"chat", userQuestion:"Di aspek mana performa STAR dan FACT saya paling menonjol?", evaluationContext:"&lt;eval_data&gt;", history:[]}</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200
+    <t>HTTP 200
 JSON: {text: string (length &gt; 20)}
 Respons kontekstual (menyebut nama/skor)</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200 ✓
+    <t>HTTP 200 ✓
 text: 1.151 chars
 Opening: "Halo Avit, senang sekali melihat hasil evaluasi Anda..."
 Kontekstual terhadap evaluasi</t>
@@ -1428,7 +1445,7 @@
     <t>TC-API-08</t>
   </si>
   <si>
-    <t xml:space="preserve">POST
+    <t>POST
 /api/coaching
 (action: speech)</t>
   </si>
@@ -1439,11 +1456,11 @@
     <t>{action:"speech", text:"Halo Mas Avit, selamat atas hasil evaluasi wawancaranya yang sangat solid."}</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200
+    <t>HTTP 200
 JSON: {audioData: base64_string, mimeType: "audio/L16;..."}</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200 ✓
+    <t>HTTP 200 ✓
 audioData: 333.504 chars base64
 mimeType: "audio/L16;codec=pcm;rate=24000"
 (PCM 24kHz valid)</t>
@@ -1452,23 +1469,23 @@
     <t>TC-API-09</t>
   </si>
   <si>
-    <t xml:space="preserve">POST
+    <t>POST
 /api/coaching
 (action: practice)</t>
   </si>
   <si>
-    <t xml:space="preserve">Positif: Practice retry comparison
+    <t>Positif: Practice retry comparison
 jawaban lama vs baru</t>
   </si>
   <si>
     <t>{action:"practice", question:"...", originalAnswer:"Saya cari bugnya di log...", newAnswer:"Waktu itu terjadi memory leak di production... Chrome DevTools..."}</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200
+    <t>HTTP 200
 JSON: {is_better:boolean, rating:number, star:{score,...}, concise:{...}, improvement_note:string}</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200 ✓
+    <t>HTTP 200 ✓
 is_better: true
 Rating baru: 8/10
 STAR: 3/4
@@ -1478,24 +1495,24 @@
     <t>TC-API-10</t>
   </si>
   <si>
-    <t xml:space="preserve">POST
+    <t>POST
 /api/coaching
 (action: highlight)</t>
   </si>
   <si>
-    <t xml:space="preserve">Positif: Generate ulasan lisan
+    <t>Positif: Generate ulasan lisan
 untuk jawaban pendek</t>
   </si>
   <si>
     <t>{action:"highlight", question:"Bagaimana mengelola state?", userAnswer:"Saya pakai Zustand dan React Query.", suggestion:"...", hack:"..."}</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200
+    <t>HTTP 200
 JSON: {text: string (length &gt; 20)}
 Ulasan personal, spesifik</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200 ✓
+    <t>HTTP 200 ✓
 text: 751 chars
 Opening: "Wah, jujur ya, jawaban kamu tadi tuh to the point banget..."</t>
   </si>
@@ -1503,7 +1520,7 @@
     <t>7.743 ms</t>
   </si>
   <si>
-    <t xml:space="preserve">LAPISAN 3 — END-TO-END TESTING (Playwright Headless)
+    <t>LAPISAN 3 — END-TO-END TESTING (Playwright Headless)
 Script: hasil_pengujian/scripts/test_e2e_playwright.mjs  |  Browser: Chrome for Testing 156.0.8078.4  |  Playwright 1.64.1</t>
   </si>
   <si>
@@ -1522,27 +1539,27 @@
     <t>Landing Page Load &amp; Elemen Utama</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Buka http://localhost:3000
+    <t>1. Buka http://localhost:3000
 2. Tunggu networkidle
 3. Ambil title, H1, URL akhir
 4. Cek tombol login &amp; upload area
 5. Screenshot fullpage</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200
+    <t>HTTP 200
 Title mengandung "Intervyou"
 H1 terisi
 URL: http://localhost:3000/
 Halaman ter-render penuh</t>
   </si>
   <si>
-    <t xml:space="preserve">URL akhir: http://localhost:3000/ ✓
+    <t>URL akhir: http://localhost:3000/ ✓
 Title: "Intervyou | AI Interview Simulator" ✓
 H1: "AI InterviewSimulator" ✓
 Halaman ter-render</t>
   </si>
   <si>
-    <t xml:space="preserve">e2e01_landing_page.png
+    <t>e2e01_landing_page.png
 (1.1 MB, fullpage 1280px)</t>
   </si>
   <si>
@@ -1552,26 +1569,26 @@
     <t>Halaman Login — Form &amp; Tombol Tersedia</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Buka http://localhost:3000/login
+    <t>1. Buka http://localhost:3000/login
 2. Tunggu networkidle
 3. Cek tombol Google OAuth
 4. Cek teks login
 5. Screenshot</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP 200
+    <t>HTTP 200
 Tombol Google OAuth ada
 Teks "masuk/login/google" ditemukan
 Form auth ada</t>
   </si>
   <si>
-    <t xml:space="preserve">URL: http://localhost:3000/login ✓
+    <t>URL: http://localhost:3000/login ✓
 Tombol Google: 1 element ✓
 Teks "Masuk/Google" ditemukan ✓
 Title: "Intervyou | AI Interview Simulator"</t>
   </si>
   <si>
-    <t xml:space="preserve">e2e02_login_page.png
+    <t>e2e02_login_page.png
 (185 KB)</t>
   </si>
   <si>
@@ -1581,7 +1598,7 @@
     <t>Responsivitas Mobile View (390px)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Set viewport: 390x844 (iPhone 14)
+    <t>1. Set viewport: 390x844 (iPhone 14)
 2. Buka http://localhost:3000
 3. Ukur document.body.scrollWidth
 4. Bandingkan dengan viewport 390px
@@ -1589,18 +1606,18 @@
 6. Screenshot</t>
   </si>
   <si>
-    <t xml:space="preserve">body.scrollWidth = 390px (= viewport)
+    <t>body.scrollWidth = 390px (= viewport)
 Tidak ada horizontal scroll
 Konten ter-render di mobile</t>
   </si>
   <si>
-    <t xml:space="preserve">Body width: 390px = viewport ✓
+    <t>Body width: 390px = viewport ✓
 Horizontal scroll: TIDAK ADA ✓
 Konten terisi: Ya ✓
 Fully responsive</t>
   </si>
   <si>
-    <t xml:space="preserve">e2e03_mobile_view.png
+    <t>e2e03_mobile_view.png
 (468 KB, mobile view)</t>
   </si>
   <si>
@@ -1610,27 +1627,27 @@
     <t>Performa Halaman (Navigation Timing API)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Buka http://localhost:3000
+    <t>1. Buka http://localhost:3000
 2. Tunggu event "load"
 3. Query window.performance Navigation Timing
 4. Hitung TTFB, DOMContentLoaded, Full Load
 5. Screenshot</t>
   </si>
   <si>
-    <t xml:space="preserve">Full Load &lt; 5000ms
+    <t>Full Load &lt; 5000ms
 TTFB terukur
 DOM Ready terukur
 Ada data performa</t>
   </si>
   <si>
-    <t xml:space="preserve">TTFB: 1.636ms ✓
+    <t>TTFB: 1.636ms ✓
 DOM Ready: 2.129ms ✓
 Full Load: 2.759ms ✓
 Semua &lt; 5000ms threshold
 (Dev mode, prod lebih cepat)</t>
   </si>
   <si>
-    <t xml:space="preserve">e2e04_performance.png
+    <t>e2e04_performance.png
 (208 KB)</t>
   </si>
   <si>
@@ -1664,11 +1681,11 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t xml:space="preserve">Pada beban pengujian tinggi (&gt;5 request/menit ke Gemini), endpoint /api/coaching (action: chat) mengembalikan HTTP 429 RESOURCE_EXHAUSTED dengan pesan: "Quota exceeded for metric: GenerateRequestsPerMinutePerProjectPerModel-FreeTier". Limit: 5 req/menit untuk model gemini-3-flash free tier.
+    <t>Pada beban pengujian tinggi (&gt;5 request/menit ke Gemini), endpoint /api/coaching (action: chat) mengembalikan HTTP 429 RESOURCE_EXHAUSTED dengan pesan: "Quota exceeded for metric: GenerateRequestsPerMinutePerProjectPerModel-FreeTier". Limit: 5 req/menit untuk model gemini-3-flash free tier.
 Catatan: Kode sudah menangani error dengan benar (tidak crash, return JSON error terstruktur). Masalah ini bersifat kondisional dan HANYA muncul saat beban tinggi.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Upgrade API key Gemini ke tier berbayar untuk production.
+    <t>1. Upgrade API key Gemini ke tier berbayar untuk production.
 2. Implementasi request queue dengan exponential backoff (sudah ada sebagian di withRetry()).
 3. Tambahkan client-side rate limiter untuk batasi panggilan coaching maksimal 1x per 10 detik.
 4. Tampilkan pesan user-friendly "Siti sedang sibuk, coba lagi dalam 30 detik" saat 429.</t>
@@ -1689,7 +1706,7 @@
     <t>Saat menerima input kosong {type:"cv", input:{}}, endpoint /api/extract mengembalikan HTTP 200 (OK) alih-alih HTTP 400 (Bad Request) atau HTTP 422 (Unprocessable Entity). Dari sudut REST API design, response 200 untuk request invalid adalah tidak tepat secara semantik, meskipun tidak menyebabkan crash atau perilaku berbahaya.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tambahkan validasi input di awal handler POST:
+    <t>1. Tambahkan validasi input di awal handler POST:
    if (!body.input?.file?.base64) return NextResponse.json({error: "File base64 required"}, {status: 400})
 2. Return HTTP 400 dengan pesan error yang informatif.
 3. Dokumentasikan schema request yang diharapkan.</t>
@@ -1704,11 +1721,11 @@
     <t>INFO</t>
   </si>
   <si>
-    <t xml:space="preserve">Semua response time diukur di environment development (npm run dev) dengan Next.js compiler aktif. TTFB landing page: 1.636ms, yang tergolong lambat untuk production. Ini adalah karakteristik normal Next.js dev mode (tidak ada optimasi build, ada hot-reload overhead, JIT compilation).
+    <t>Semua response time diukur di environment development (npm run dev) dengan Next.js compiler aktif. TTFB landing page: 1.636ms, yang tergolong lambat untuk production. Ini adalah karakteristik normal Next.js dev mode (tidak ada optimasi build, ada hot-reload overhead, JIT compilation).
 Di production build (next build + next start), TTFB diproyeksikan &lt;200ms.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Jalankan pengujian performa di production build untuk angka yang akurat.
+    <t>1. Jalankan pengujian performa di production build untuk angka yang akurat.
 2. Tambahkan next/image optimization untuk gambar besar.
 3. Aktifkan ISR (Incremental Static Regeneration) untuk halaman yang memungkinkan.
 4. Gunakan CDN untuk static assets di production.</t>
@@ -1723,7 +1740,7 @@
     <t>Pengujian tidak mencakup alur login Google OAuth secara otomatis karena Playwright tidak dapat berinteraksi dengan popup Google OAuth eksternal (domain google.com, keamanan popup). Halaman /login dan keberadaan tombol Google OAuth sudah diverifikasi (TC-E2E-02), namun alur lengkap Google OAuth → Firebase → redirect tidak diuji secara otomatis.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Untuk E2E auth testing, gunakan Firebase Auth Emulator (firebase emulators:start).
+    <t>1. Untuk E2E auth testing, gunakan Firebase Auth Emulator (firebase emulators:start).
 2. Buat custom Firebase auth token di test setup untuk bypass OAuth popup.
 3. Tambahkan unit test untuk AuthContext.tsx menggunakan jest + firebase testing library.
 4. Untuk testing manual, dokumenkan langkah-langkah verifikasi auth.</t>
@@ -1738,13 +1755,13 @@
     <t>Fitur Live Interview Voice-to-Voice (F-09 s/d F-13) memerlukan akses mikrofon browser dan WebSocket ke Gemini Live API. Browser headless Playwright tidak mendukung akses mikrofon nyata. Pengujian audio (TC-UNIT-07, TC-UNIT-08) sudah memverifikasi format WAV yang dihasilkan, dan TC-API-01 sudah memverifikasi token generation.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Untuk pengujian audio, gunakan Playwright mock MediaStream/MediaRecorder API.
+    <t>1. Untuk pengujian audio, gunakan Playwright mock MediaStream/MediaRecorder API.
 2. Simulasikan WebSocket message menggunakan fixtures audio pre-recorded.
 3. Tambahkan integration test untuk audio-manager.ts dengan Node.js audio buffer mock.
 4. Lakukan pengujian manual dengan scenario script terstandar.</t>
   </si>
   <si>
-    <t xml:space="preserve">DETAIL SKOR EVALUASI LLM-as-a-Judge (TC-API-06)
+    <t>DETAIL SKOR EVALUASI LLM-as-a-Judge (TC-API-06)
 Output dari POST /api/evaluate — Transkrip 7 Pertanyaan BEI Kandidat Avit Febriansyah</t>
   </si>
   <si>
@@ -1790,53 +1807,53 @@
     <t>B. SKOR PER PERTANYAAN — STAR, FACT, ConCISE, &amp; SPENCER FRAMEWORK</t>
   </si>
   <si>
-    <t xml:space="preserve">Kompetensi
+    <t>Kompetensi
 Spencer</t>
   </si>
   <si>
     <t>Ringkasan Pertanyaan BEI</t>
   </si>
   <si>
-    <t xml:space="preserve">STAR
+    <t>STAR
 Score
 (/4)</t>
   </si>
   <si>
-    <t xml:space="preserve">FACT
+    <t>FACT
 Feeling
 (/10)</t>
   </si>
   <si>
-    <t xml:space="preserve">FACT
+    <t>FACT
 Action
 (/10)</t>
   </si>
   <si>
-    <t xml:space="preserve">FACT
+    <t>FACT
 Context
 (/10)</t>
   </si>
   <si>
-    <t xml:space="preserve">FACT
+    <t>FACT
 Thinking
 (/10)</t>
   </si>
   <si>
-    <t xml:space="preserve">FACT
+    <t>FACT
 Total
 (/40)</t>
   </si>
   <si>
-    <t xml:space="preserve">ConCISE
+    <t>ConCISE
 Total
 (/25)</t>
   </si>
   <si>
-    <t xml:space="preserve">Rating
+    <t>Rating
 (/10)</t>
   </si>
   <si>
-    <t xml:space="preserve">Spencer
+    <t>Spencer
 Level
 (/5)</t>
   </si>
@@ -1847,7 +1864,7 @@
     <t>Q1</t>
   </si>
   <si>
-    <t xml:space="preserve">EXP
+    <t>EXP
 (Technical Expertise)</t>
   </si>
   <si>
@@ -1875,7 +1892,7 @@
     <t>Q2</t>
   </si>
   <si>
-    <t xml:space="preserve">AT
+    <t>AT
 (Analytical Thinking)</t>
   </si>
   <si>
@@ -1894,7 +1911,7 @@
     <t>Q3</t>
   </si>
   <si>
-    <t xml:space="preserve">CT
+    <t>CT
 (Conceptual Thinking)</t>
   </si>
   <si>
@@ -1919,7 +1936,7 @@
     <t>Q4</t>
   </si>
   <si>
-    <t xml:space="preserve">ACH
+    <t>ACH
 (Achievement Orientation)</t>
   </si>
   <si>
@@ -2088,110 +2105,116 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="15"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="10"/>
+      <color rgb="FF0F0F1A"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF155724"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF6C757D"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF155724"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
+      <sz val="10"/>
       <color rgb="FF0F0F1A"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF155724"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF6C757D"/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF155724"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF0F0F1A"/>
       <sz val="10"/>
+      <color rgb="FF155724"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FF155724"/>
-      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF155724"/>
-      <sz val="11"/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0C5460"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="13"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
+      <sz val="10"/>
       <color rgb="FF0C5460"/>
-      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF0C5460"/>
       <sz val="10"/>
+      <color rgb="FF856404"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF856404"/>
-      <sz val="10"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="9"/>
+      <sz val="10"/>
+      <color rgb="FF856404"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF856404"/>
-      <sz val="10"/>
+      <sz val="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="17">
@@ -2334,8 +2357,200 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2345,233 +2560,47 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2911,433 +2940,434 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:H26"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" ht="44" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:8" ht="44.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="65" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-    </row>
-    <row r="3" ht="22" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+    </row>
+    <row r="3" spans="2:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="3" t="s">
+      <c r="C3" s="66"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+    </row>
+    <row r="5" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" ht="32" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+    </row>
+    <row r="6" spans="2:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
+    <row r="7" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="2">
         <v>10</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="4">
         <v>10</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B8" s="10" t="s">
+    <row r="8" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="7">
         <v>10</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="4">
         <v>10</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
+    <row r="9" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="2">
         <v>4</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="4">
         <v>4</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="13" t="s">
+    <row r="10" spans="2:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="10">
         <v>24</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="12">
         <v>24</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" ht="10" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B13" s="18" t="s">
+    <row r="12" spans="2:8" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-    </row>
-    <row r="14" ht="26" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
+    </row>
+    <row r="14" spans="2:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="19" t="s">
+    <row r="15" spans="2:8" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G15" s="20" t="s">
+      <c r="G15" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="21" t="s">
+    <row r="16" spans="2:8" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="G16" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="19" t="s">
+    <row r="17" spans="2:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="20" t="s">
+      <c r="G17" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="21" t="s">
+    <row r="18" spans="2:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="20" t="s">
+      <c r="G18" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="19" t="s">
+    <row r="19" spans="2:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="20" t="s">
+      <c r="G19" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="21" t="s">
+    <row r="20" spans="2:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="20" t="s">
+      <c r="G20" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="19" t="s">
+    <row r="21" spans="2:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G21" s="20" t="s">
+      <c r="G21" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="21" t="s">
+    <row r="22" spans="2:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="G22" s="20" t="s">
+      <c r="G22" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="19" t="s">
+    <row r="23" spans="2:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="G23" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="21" t="s">
+    <row r="24" spans="2:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G24" s="20" t="s">
+      <c r="G24" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="19" t="s">
+    <row r="25" spans="2:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="G25" s="20" t="s">
+      <c r="G25" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="21" t="s">
+    <row r="26" spans="2:7" ht="62.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G26" s="20" t="s">
+      <c r="G26" s="16" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3348,15 +3378,16 @@
     <mergeCell ref="B5:G5"/>
     <mergeCell ref="B13:H13"/>
   </mergeCells>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:C38"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
@@ -3364,259 +3395,259 @@
     <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="36" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="22" t="s">
+    <row r="2" spans="2:3" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="70" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="22"/>
-    </row>
-    <row r="4" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="23" t="s">
+      <c r="C2" s="70"/>
+    </row>
+    <row r="4" spans="2:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="C4" s="23"/>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
+      <c r="C4" s="69"/>
+    </row>
+    <row r="5" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="25" t="s">
+    <row r="6" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="20" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="24" t="s">
+    <row r="7" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="23" t="s">
+    <row r="9" spans="2:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="23"/>
-    </row>
-    <row r="10" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="25" t="s">
+      <c r="C9" s="69"/>
+    </row>
+    <row r="10" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="20" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="24" t="s">
+    <row r="11" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="25" t="s">
+    <row r="12" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="20" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="23" t="s">
+    <row r="14" spans="2:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="69" t="s">
         <v>93</v>
       </c>
-      <c r="C14" s="23"/>
-    </row>
-    <row r="15" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="24" t="s">
+      <c r="C14" s="69"/>
+    </row>
+    <row r="15" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="25" t="s">
+    <row r="16" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="20" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="24" t="s">
+    <row r="17" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="25" t="s">
+    <row r="18" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="20" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="24" t="s">
+    <row r="19" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="25" t="s">
+    <row r="20" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="20" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="24" t="s">
+    <row r="21" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B23" s="23" t="s">
+    <row r="23" spans="2:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="69" t="s">
         <v>108</v>
       </c>
-      <c r="C23" s="23"/>
-    </row>
-    <row r="24" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B24" s="25" t="s">
+      <c r="C23" s="69"/>
+    </row>
+    <row r="24" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="20" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B25" s="24" t="s">
+    <row r="25" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B26" s="25" t="s">
+    <row r="26" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="20" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B27" s="24" t="s">
+    <row r="27" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B29" s="23" t="s">
+    <row r="29" spans="2:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="C29" s="23"/>
-    </row>
-    <row r="30" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B30" s="25" t="s">
+      <c r="C29" s="69"/>
+    </row>
+    <row r="30" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="20" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B31" s="24" t="s">
+    <row r="31" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="25" t="s">
+    <row r="32" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="C32" s="26" t="s">
+      <c r="C32" s="20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B33" s="24" t="s">
+    <row r="33" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="35" ht="22" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B35" s="23" t="s">
+    <row r="35" spans="2:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="69" t="s">
         <v>126</v>
       </c>
-      <c r="C35" s="23"/>
-    </row>
-    <row r="36" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B36" s="25" t="s">
+      <c r="C35" s="69"/>
+    </row>
+    <row r="36" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C36" s="20" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B37" s="24" t="s">
+    <row r="37" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B38" s="25" t="s">
+    <row r="38" spans="2:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="20" t="s">
         <v>132</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B35:C35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:K29"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -3629,829 +3660,829 @@
     <col min="11" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="36" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="27" t="s">
+    <row r="2" spans="2:11" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="71" t="s">
         <v>133</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B3" s="28" t="s">
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+    </row>
+    <row r="3" spans="2:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="72" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-    </row>
-    <row r="5" ht="26" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="29" t="s">
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+    </row>
+    <row r="5" spans="2:11" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="29" t="s">
+      <c r="D5" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="J5" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="K5" s="29" t="s">
+      <c r="K5" s="21" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="6" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="19" t="s">
+    <row r="6" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="H6" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="I6" s="31" t="s">
+      <c r="I6" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="31" t="s">
+      <c r="J6" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="K6" s="20" t="s">
+      <c r="K6" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="33" t="s">
+    <row r="7" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="D7" s="34" t="s">
+      <c r="D7" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="G7" s="36" t="s">
+      <c r="G7" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="H7" s="37" t="s">
+      <c r="H7" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="I7" s="35" t="s">
+      <c r="I7" s="27" t="s">
         <v>157</v>
       </c>
-      <c r="J7" s="35" t="s">
+      <c r="J7" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="K7" s="20" t="s">
+      <c r="K7" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="19" t="s">
+    <row r="8" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="I8" s="31" t="s">
+      <c r="I8" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="J8" s="31" t="s">
+      <c r="J8" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="K8" s="20" t="s">
+      <c r="K8" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="33" t="s">
+    <row r="9" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D9" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="G9" s="36" t="s">
+      <c r="G9" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="H9" s="37" t="s">
+      <c r="H9" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="I9" s="35" t="s">
+      <c r="I9" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="J9" s="35" t="s">
+      <c r="J9" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="K9" s="20" t="s">
+      <c r="K9" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="19" t="s">
+    <row r="10" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="H10" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="I10" s="31" t="s">
+      <c r="I10" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="J10" s="31" t="s">
+      <c r="J10" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="K10" s="20" t="s">
+      <c r="K10" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="33" t="s">
+    <row r="11" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D11" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="27" t="s">
         <v>184</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="G11" s="36" t="s">
+      <c r="G11" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="H11" s="37" t="s">
+      <c r="H11" s="29" t="s">
         <v>187</v>
       </c>
-      <c r="I11" s="35" t="s">
+      <c r="I11" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="J11" s="35" t="s">
+      <c r="J11" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="K11" s="20" t="s">
+      <c r="K11" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="19" t="s">
+    <row r="12" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C12" s="30" t="s">
+      <c r="C12" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H12" s="32" t="s">
+      <c r="H12" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="I12" s="31" t="s">
+      <c r="I12" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="J12" s="31" t="s">
+      <c r="J12" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="K12" s="20" t="s">
+      <c r="K12" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="33" t="s">
+    <row r="13" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D13" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="27" t="s">
         <v>197</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="28" t="s">
         <v>198</v>
       </c>
-      <c r="G13" s="36" t="s">
+      <c r="G13" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="H13" s="37" t="s">
+      <c r="H13" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="I13" s="35" t="s">
+      <c r="I13" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="J13" s="35" t="s">
+      <c r="J13" s="27" t="s">
         <v>202</v>
       </c>
-      <c r="K13" s="20" t="s">
+      <c r="K13" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="19" t="s">
+    <row r="14" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="C14" s="30" t="s">
+      <c r="C14" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="H14" s="32" t="s">
+      <c r="H14" s="24" t="s">
         <v>208</v>
       </c>
-      <c r="I14" s="31" t="s">
+      <c r="I14" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="J14" s="31" t="s">
+      <c r="J14" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="K14" s="20" t="s">
+      <c r="K14" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="15" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="33" t="s">
+    <row r="15" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D15" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="G15" s="36" t="s">
+      <c r="G15" s="28" t="s">
         <v>216</v>
       </c>
-      <c r="H15" s="37" t="s">
+      <c r="H15" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="I15" s="35" t="s">
+      <c r="I15" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="J15" s="35" t="s">
+      <c r="J15" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="K15" s="20" t="s">
+      <c r="K15" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="19" t="s">
+    <row r="16" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="C16" s="38" t="s">
+      <c r="C16" s="30" t="s">
         <v>212</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D16" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="H16" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="I16" s="31" t="s">
+      <c r="I16" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="J16" s="31" t="s">
+      <c r="J16" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="K16" s="20" t="s">
+      <c r="K16" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="33" t="s">
+    <row r="17" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="25" t="s">
         <v>226</v>
       </c>
-      <c r="D17" s="34" t="s">
+      <c r="D17" s="26" t="s">
         <v>227</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="G17" s="36" t="s">
+      <c r="G17" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="H17" s="37" t="s">
+      <c r="H17" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="I17" s="35" t="s">
+      <c r="I17" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="J17" s="35" t="s">
+      <c r="J17" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="K17" s="20" t="s">
+      <c r="K17" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="19" t="s">
+    <row r="18" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="C18" s="30" t="s">
+      <c r="C18" s="22" t="s">
         <v>233</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="18" t="s">
         <v>234</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="I18" s="31" t="s">
+      <c r="I18" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="J18" s="31" t="s">
+      <c r="J18" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="K18" s="20" t="s">
+      <c r="K18" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="33" t="s">
+    <row r="19" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="D19" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="E19" s="35" t="s">
+      <c r="E19" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="F19" s="28" t="s">
         <v>242</v>
       </c>
-      <c r="G19" s="36" t="s">
+      <c r="G19" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="H19" s="37" t="s">
+      <c r="H19" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="I19" s="35" t="s">
+      <c r="I19" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="J19" s="35" t="s">
+      <c r="J19" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="K19" s="20" t="s">
+      <c r="K19" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="19" t="s">
+    <row r="20" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="E20" s="31" t="s">
+      <c r="E20" s="23" t="s">
         <v>247</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="H20" s="32" t="s">
+      <c r="H20" s="24" t="s">
         <v>250</v>
       </c>
-      <c r="I20" s="31" t="s">
+      <c r="I20" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="J20" s="31" t="s">
+      <c r="J20" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="K20" s="20" t="s">
+      <c r="K20" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="21" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="33" t="s">
+    <row r="21" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="25" t="s">
         <v>251</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="25" t="s">
         <v>252</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="D21" s="26" t="s">
         <v>253</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="E21" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="F21" s="36" t="s">
+      <c r="F21" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="G21" s="36" t="s">
+      <c r="G21" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="H21" s="37" t="s">
+      <c r="H21" s="29" t="s">
         <v>257</v>
       </c>
-      <c r="I21" s="35" t="s">
+      <c r="I21" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="J21" s="35" t="s">
+      <c r="J21" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="K21" s="20" t="s">
+      <c r="K21" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="22" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="19" t="s">
+    <row r="22" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="24" t="s">
+      <c r="D22" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="E22" s="31" t="s">
+      <c r="E22" s="23" t="s">
         <v>262</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="H22" s="32" t="s">
+      <c r="H22" s="24" t="s">
         <v>265</v>
       </c>
-      <c r="I22" s="31" t="s">
+      <c r="I22" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="J22" s="31" t="s">
+      <c r="J22" s="23" t="s">
         <v>266</v>
       </c>
-      <c r="K22" s="20" t="s">
+      <c r="K22" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="33" t="s">
+    <row r="23" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="34" t="s">
+      <c r="D23" s="26" t="s">
         <v>268</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E23" s="27" t="s">
         <v>269</v>
       </c>
-      <c r="F23" s="36" t="s">
+      <c r="F23" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="G23" s="36" t="s">
+      <c r="G23" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="H23" s="37" t="s">
+      <c r="H23" s="29" t="s">
         <v>272</v>
       </c>
-      <c r="I23" s="35" t="s">
+      <c r="I23" s="27" t="s">
         <v>273</v>
       </c>
-      <c r="J23" s="35" t="s">
+      <c r="J23" s="27" t="s">
         <v>266</v>
       </c>
-      <c r="K23" s="20" t="s">
+      <c r="K23" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="24" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="19" t="s">
+    <row r="24" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="E24" s="23" t="s">
         <v>276</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="H24" s="32" t="s">
+      <c r="H24" s="24" t="s">
         <v>279</v>
       </c>
-      <c r="I24" s="31" t="s">
+      <c r="I24" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="J24" s="31" t="s">
+      <c r="J24" s="23" t="s">
         <v>266</v>
       </c>
-      <c r="K24" s="20" t="s">
+      <c r="K24" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="25" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="33" t="s">
+    <row r="25" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="34" t="s">
+      <c r="D25" s="26" t="s">
         <v>281</v>
       </c>
-      <c r="E25" s="35" t="s">
+      <c r="E25" s="27" t="s">
         <v>282</v>
       </c>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="28" t="s">
         <v>283</v>
       </c>
-      <c r="G25" s="36" t="s">
+      <c r="G25" s="28" t="s">
         <v>284</v>
       </c>
-      <c r="H25" s="37" t="s">
+      <c r="H25" s="29" t="s">
         <v>279</v>
       </c>
-      <c r="I25" s="35" t="s">
+      <c r="I25" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="J25" s="35" t="s">
+      <c r="J25" s="27" t="s">
         <v>266</v>
       </c>
-      <c r="K25" s="20" t="s">
+      <c r="K25" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="26" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="19" t="s">
+    <row r="26" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="C26" s="30" t="s">
+      <c r="C26" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="D26" s="24" t="s">
+      <c r="D26" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="E26" s="31" t="s">
+      <c r="E26" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="H26" s="32" t="s">
+      <c r="H26" s="24" t="s">
         <v>290</v>
       </c>
-      <c r="I26" s="31" t="s">
+      <c r="I26" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="J26" s="31" t="s">
+      <c r="J26" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="K26" s="20" t="s">
+      <c r="K26" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="33" t="s">
+    <row r="27" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="C27" s="30" t="s">
+      <c r="C27" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="D27" s="34" t="s">
+      <c r="D27" s="26" t="s">
         <v>294</v>
       </c>
-      <c r="E27" s="35" t="s">
+      <c r="E27" s="27" t="s">
         <v>295</v>
       </c>
-      <c r="F27" s="36" t="s">
+      <c r="F27" s="28" t="s">
         <v>296</v>
       </c>
-      <c r="G27" s="36" t="s">
+      <c r="G27" s="28" t="s">
         <v>297</v>
       </c>
-      <c r="H27" s="37" t="s">
+      <c r="H27" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="I27" s="35" t="s">
+      <c r="I27" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="J27" s="35" t="s">
+      <c r="J27" s="27" t="s">
         <v>299</v>
       </c>
-      <c r="K27" s="20" t="s">
+      <c r="K27" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="28" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="19" t="s">
+    <row r="28" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="31" t="s">
         <v>301</v>
       </c>
-      <c r="D28" s="24" t="s">
+      <c r="D28" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="E28" s="31" t="s">
+      <c r="E28" s="23" t="s">
         <v>303</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="F28" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="H28" s="32" t="s">
+      <c r="H28" s="24" t="s">
         <v>306</v>
       </c>
-      <c r="I28" s="31" t="s">
+      <c r="I28" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="J28" s="31" t="s">
+      <c r="J28" s="23" t="s">
         <v>307</v>
       </c>
-      <c r="K28" s="20" t="s">
+      <c r="K28" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="29" ht="55" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="33" t="s">
+    <row r="29" spans="2:11" ht="54.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="25" t="s">
         <v>308</v>
       </c>
-      <c r="C29" s="39" t="s">
+      <c r="C29" s="31" t="s">
         <v>309</v>
       </c>
-      <c r="D29" s="34" t="s">
+      <c r="D29" s="26" t="s">
         <v>310</v>
       </c>
-      <c r="E29" s="35" t="s">
+      <c r="E29" s="27" t="s">
         <v>311</v>
       </c>
-      <c r="F29" s="36" t="s">
+      <c r="F29" s="28" t="s">
         <v>312</v>
       </c>
-      <c r="G29" s="36" t="s">
+      <c r="G29" s="28" t="s">
         <v>313</v>
       </c>
-      <c r="H29" s="37" t="s">
+      <c r="H29" s="29" t="s">
         <v>314</v>
       </c>
-      <c r="I29" s="35" t="s">
+      <c r="I29" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="J29" s="35" t="s">
+      <c r="J29" s="27" t="s">
         <v>299</v>
       </c>
-      <c r="K29" s="20" t="s">
+      <c r="K29" s="16" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4461,14 +4492,14 @@
     <mergeCell ref="B3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:I14"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -4479,300 +4510,300 @@
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="36" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+    <row r="2" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="67" t="s">
         <v>316</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="4" ht="26" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="40" t="s">
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+    </row>
+    <row r="4" spans="2:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="32" t="s">
         <v>317</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="32" t="s">
         <v>318</v>
       </c>
-      <c r="E4" s="40" t="s">
+      <c r="E4" s="32" t="s">
         <v>319</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="F4" s="32" t="s">
         <v>320</v>
       </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="32" t="s">
         <v>321</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="32" t="s">
         <v>322</v>
       </c>
-      <c r="I4" s="40" t="s">
+      <c r="I4" s="32" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
+    <row r="5" spans="2:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="18" t="s">
         <v>323</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="24" t="s">
         <v>325</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="23" t="s">
         <v>326</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="H5" s="41" t="s">
+      <c r="H5" s="33" t="s">
         <v>328</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="42" t="s">
+    <row r="6" spans="2:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="35" t="s">
         <v>330</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="36" t="s">
         <v>325</v>
       </c>
-      <c r="F6" s="45" t="s">
+      <c r="F6" s="37" t="s">
         <v>331</v>
       </c>
-      <c r="G6" s="43" t="s">
+      <c r="G6" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="H6" s="41" t="s">
+      <c r="H6" s="33" t="s">
         <v>333</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
+    <row r="7" spans="2:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="18" t="s">
         <v>334</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="24" t="s">
         <v>325</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="F7" s="23" t="s">
         <v>336</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="33" t="s">
         <v>338</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="42" t="s">
+    <row r="8" spans="2:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="34" t="s">
         <v>339</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="36" t="s">
         <v>325</v>
       </c>
-      <c r="F8" s="45" t="s">
+      <c r="F8" s="37" t="s">
         <v>342</v>
       </c>
-      <c r="G8" s="43" t="s">
+      <c r="G8" s="35" t="s">
         <v>343</v>
       </c>
-      <c r="H8" s="41" t="s">
+      <c r="H8" s="33" t="s">
         <v>344</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
+    <row r="9" spans="2:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="E9" s="24" t="s">
         <v>325</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="F9" s="23" t="s">
         <v>348</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="H9" s="41" t="s">
+      <c r="H9" s="33" t="s">
         <v>350</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="42" t="s">
+    <row r="10" spans="2:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="34" t="s">
         <v>351</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="D10" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="36" t="s">
         <v>325</v>
       </c>
-      <c r="F10" s="45" t="s">
+      <c r="F10" s="37" t="s">
         <v>354</v>
       </c>
-      <c r="G10" s="43" t="s">
+      <c r="G10" s="35" t="s">
         <v>355</v>
       </c>
-      <c r="H10" s="41" t="s">
+      <c r="H10" s="33" t="s">
         <v>356</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="I10" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
+    <row r="11" spans="2:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="18" t="s">
         <v>358</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="24" t="s">
         <v>360</v>
       </c>
-      <c r="F11" s="31" t="s">
+      <c r="F11" s="23" t="s">
         <v>361</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="H11" s="41" t="s">
+      <c r="H11" s="33" t="s">
         <v>363</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="42" t="s">
+    <row r="12" spans="2:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="34" t="s">
         <v>364</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="35" t="s">
         <v>366</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="36" t="s">
         <v>360</v>
       </c>
-      <c r="F12" s="45" t="s">
+      <c r="F12" s="37" t="s">
         <v>367</v>
       </c>
-      <c r="G12" s="43" t="s">
+      <c r="G12" s="35" t="s">
         <v>368</v>
       </c>
-      <c r="H12" s="41" t="s">
+      <c r="H12" s="33" t="s">
         <v>369</v>
       </c>
-      <c r="I12" s="20" t="s">
+      <c r="I12" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
+    <row r="13" spans="2:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="18" t="s">
         <v>371</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="24" t="s">
         <v>373</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="23" t="s">
         <v>374</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="H13" s="41" t="s">
+      <c r="H13" s="33" t="s">
         <v>375</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" ht="48" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="42" t="s">
+    <row r="14" spans="2:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="34" t="s">
         <v>376</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="D14" s="43" t="s">
+      <c r="D14" s="35" t="s">
         <v>378</v>
       </c>
-      <c r="E14" s="44" t="s">
+      <c r="E14" s="36" t="s">
         <v>373</v>
       </c>
-      <c r="F14" s="45" t="s">
+      <c r="F14" s="37" t="s">
         <v>379</v>
       </c>
-      <c r="G14" s="43" t="s">
+      <c r="G14" s="35" t="s">
         <v>380</v>
       </c>
-      <c r="H14" s="41" t="s">
+      <c r="H14" s="33" t="s">
         <v>381</v>
       </c>
-      <c r="I14" s="20" t="s">
+      <c r="I14" s="16" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4781,14 +4812,14 @@
     <mergeCell ref="B2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:I14"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -4799,301 +4830,301 @@
     <col min="8" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="36" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="46" t="s">
+    <row r="2" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="73" t="s">
         <v>382</v>
       </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-    </row>
-    <row r="4" ht="26" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="47" t="s">
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+    </row>
+    <row r="4" spans="2:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="38" t="s">
         <v>383</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="38" t="s">
         <v>384</v>
       </c>
-      <c r="E4" s="47" t="s">
+      <c r="E4" s="38" t="s">
         <v>385</v>
       </c>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="38" t="s">
         <v>386</v>
       </c>
-      <c r="G4" s="47" t="s">
+      <c r="G4" s="38" t="s">
         <v>387</v>
       </c>
-      <c r="H4" s="47" t="s">
+      <c r="H4" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="47" t="s">
+      <c r="I4" s="38" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
+    <row r="5" spans="2:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="18" t="s">
         <v>388</v>
       </c>
-      <c r="C5" s="48" t="s">
+      <c r="C5" s="39" t="s">
         <v>389</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="23" t="s">
         <v>391</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="33" t="s">
         <v>393</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="25" t="s">
+    <row r="6" spans="2:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="C6" s="49" t="s">
+      <c r="C6" s="40" t="s">
         <v>395</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="20" t="s">
         <v>396</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="41" t="s">
         <v>397</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="20" t="s">
         <v>398</v>
       </c>
-      <c r="G6" s="41" t="s">
+      <c r="G6" s="33" t="s">
         <v>399</v>
       </c>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="24" t="s">
+    <row r="7" spans="2:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="18" t="s">
         <v>400</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="39" t="s">
         <v>401</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="23" t="s">
         <v>403</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="G7" s="41" t="s">
+      <c r="G7" s="33" t="s">
         <v>405</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" ht="60" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="25" t="s">
+    <row r="8" spans="2:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="19" t="s">
         <v>406</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="40" t="s">
         <v>407</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="20" t="s">
         <v>408</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="41" t="s">
         <v>409</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="20" t="s">
         <v>410</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="G8" s="33" t="s">
         <v>411</v>
       </c>
-      <c r="H8" s="51" t="s">
+      <c r="H8" s="42" t="s">
         <v>412</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" ht="60" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="24" t="s">
+    <row r="9" spans="2:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="18" t="s">
         <v>413</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="39" t="s">
         <v>414</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="23" t="s">
         <v>416</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="G9" s="33" t="s">
         <v>418</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I9" s="20" t="s">
+      <c r="I9" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="25" t="s">
+    <row r="10" spans="2:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="19" t="s">
         <v>419</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="40" t="s">
         <v>420</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="20" t="s">
         <v>421</v>
       </c>
-      <c r="E10" s="50" t="s">
+      <c r="E10" s="41" t="s">
         <v>422</v>
       </c>
-      <c r="F10" s="26" t="s">
+      <c r="F10" s="20" t="s">
         <v>423</v>
       </c>
-      <c r="G10" s="41" t="s">
+      <c r="G10" s="33" t="s">
         <v>424</v>
       </c>
-      <c r="H10" s="51" t="s">
+      <c r="H10" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="I10" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" ht="60" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="24" t="s">
+    <row r="11" spans="2:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="18" t="s">
         <v>425</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="39" t="s">
         <v>426</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="23" t="s">
         <v>428</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="G11" s="41" t="s">
+      <c r="G11" s="33" t="s">
         <v>430</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" ht="60" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B12" s="25" t="s">
+    <row r="12" spans="2:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="19" t="s">
         <v>431</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="40" t="s">
         <v>432</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="20" t="s">
         <v>433</v>
       </c>
-      <c r="E12" s="50" t="s">
+      <c r="E12" s="41" t="s">
         <v>434</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="20" t="s">
         <v>435</v>
       </c>
-      <c r="G12" s="41" t="s">
+      <c r="G12" s="33" t="s">
         <v>436</v>
       </c>
-      <c r="H12" s="51" t="s">
+      <c r="H12" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="I12" s="20" t="s">
+      <c r="I12" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" ht="60" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B13" s="24" t="s">
+    <row r="13" spans="2:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="18" t="s">
         <v>437</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="39" t="s">
         <v>438</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="23" t="s">
         <v>440</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="G13" s="41" t="s">
+      <c r="G13" s="33" t="s">
         <v>442</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="20" t="s">
+      <c r="I13" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="25" t="s">
+    <row r="14" spans="2:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="19" t="s">
         <v>443</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="40" t="s">
         <v>444</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="20" t="s">
         <v>445</v>
       </c>
-      <c r="E14" s="50" t="s">
+      <c r="E14" s="41" t="s">
         <v>446</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F14" s="20" t="s">
         <v>447</v>
       </c>
-      <c r="G14" s="41" t="s">
+      <c r="G14" s="33" t="s">
         <v>448</v>
       </c>
-      <c r="H14" s="51" t="s">
+      <c r="H14" s="42" t="s">
         <v>449</v>
       </c>
-      <c r="I14" s="20" t="s">
+      <c r="I14" s="16" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5102,14 +5133,14 @@
     <mergeCell ref="B2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:I8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -5121,145 +5152,145 @@
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="36" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B2" s="52" t="s">
+    <row r="2" spans="2:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="74" t="s">
         <v>450</v>
       </c>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-    </row>
-    <row r="4" ht="26" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B4" s="53" t="s">
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
+      <c r="I2" s="74"/>
+    </row>
+    <row r="4" spans="2:9" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="43" t="s">
         <v>317</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="43" t="s">
         <v>384</v>
       </c>
-      <c r="D4" s="53" t="s">
+      <c r="D4" s="43" t="s">
         <v>451</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="43" t="s">
         <v>452</v>
       </c>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="43" t="s">
         <v>322</v>
       </c>
-      <c r="G4" s="53" t="s">
+      <c r="G4" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="53" t="s">
+      <c r="H4" s="43" t="s">
         <v>453</v>
       </c>
-      <c r="I4" s="53" t="s">
+      <c r="I4" s="43" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" ht="80" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
+    <row r="5" spans="2:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="18" t="s">
         <v>454</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="18" t="s">
         <v>455</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="23" t="s">
         <v>456</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="33" t="s">
         <v>458</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="32" t="s">
+      <c r="H5" s="24" t="s">
         <v>459</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="I5" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" ht="80" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="54" t="s">
+    <row r="6" spans="2:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="44" t="s">
         <v>460</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="44" t="s">
         <v>461</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="45" t="s">
         <v>462</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="E6" s="46" t="s">
         <v>463</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="33" t="s">
         <v>464</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G6" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="H6" s="58" t="s">
+      <c r="H6" s="48" t="s">
         <v>465</v>
       </c>
-      <c r="I6" s="20" t="s">
+      <c r="I6" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" ht="80" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="24" t="s">
+    <row r="7" spans="2:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="18" t="s">
         <v>466</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="18" t="s">
         <v>467</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="23" t="s">
         <v>468</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="F7" s="33" t="s">
         <v>470</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="H7" s="32" t="s">
+      <c r="H7" s="24" t="s">
         <v>471</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8" ht="80" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="54" t="s">
+    <row r="8" spans="2:9" ht="80.099999999999994" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="44" t="s">
         <v>472</v>
       </c>
-      <c r="C8" s="54" t="s">
+      <c r="C8" s="44" t="s">
         <v>473</v>
       </c>
-      <c r="D8" s="55" t="s">
+      <c r="D8" s="45" t="s">
         <v>474</v>
       </c>
-      <c r="E8" s="56" t="s">
+      <c r="E8" s="46" t="s">
         <v>475</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="33" t="s">
         <v>476</v>
       </c>
-      <c r="G8" s="57" t="s">
+      <c r="G8" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="58" t="s">
+      <c r="H8" s="48" t="s">
         <v>477</v>
       </c>
-      <c r="I8" s="20" t="s">
+      <c r="I8" s="16" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5268,14 +5299,14 @@
     <mergeCell ref="B2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:G9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -5285,133 +5316,133 @@
     <col min="7" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="36" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="59" t="s">
+    <row r="2" spans="2:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="75" t="s">
         <v>478</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-    </row>
-    <row r="4" ht="26" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="60" t="s">
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+    </row>
+    <row r="4" spans="2:7" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="49" t="s">
         <v>479</v>
       </c>
-      <c r="C4" s="60" t="s">
+      <c r="C4" s="49" t="s">
         <v>480</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="D4" s="49" t="s">
         <v>481</v>
       </c>
-      <c r="E4" s="60" t="s">
+      <c r="E4" s="49" t="s">
         <v>482</v>
       </c>
-      <c r="F4" s="60" t="s">
+      <c r="F4" s="49" t="s">
         <v>483</v>
       </c>
-      <c r="G4" s="60" t="s">
+      <c r="G4" s="49" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="5" ht="100" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
+    <row r="5" spans="2:7" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="15" t="s">
         <v>485</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="18" t="s">
         <v>486</v>
       </c>
-      <c r="D5" s="61" t="s">
+      <c r="D5" s="50" t="s">
         <v>487</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="F5" s="20" t="s">
         <v>489</v>
       </c>
-      <c r="G5" s="62" t="s">
+      <c r="G5" s="51" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="6" ht="100" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="19" t="s">
+    <row r="6" spans="2:7" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="15" t="s">
         <v>491</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="18" t="s">
         <v>492</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="52" t="s">
         <v>493</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="F6" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="53" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="7" ht="100" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="19" t="s">
+    <row r="7" spans="2:7" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="15" t="s">
         <v>496</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="18" t="s">
         <v>497</v>
       </c>
-      <c r="D7" s="65" t="s">
+      <c r="D7" s="54" t="s">
         <v>498</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="20" t="s">
         <v>500</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="53" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="8" ht="100" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="19" t="s">
+    <row r="8" spans="2:7" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="15" t="s">
         <v>501</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="18" t="s">
         <v>502</v>
       </c>
-      <c r="D8" s="61" t="s">
+      <c r="D8" s="50" t="s">
         <v>487</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="20" t="s">
         <v>504</v>
       </c>
-      <c r="G8" s="62" t="s">
+      <c r="G8" s="51" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="9" ht="100" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="19" t="s">
+    <row r="9" spans="2:7" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="15" t="s">
         <v>505</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="18" t="s">
         <v>506</v>
       </c>
-      <c r="D9" s="65" t="s">
+      <c r="D9" s="54" t="s">
         <v>498</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="F9" s="26" t="s">
+      <c r="F9" s="20" t="s">
         <v>508</v>
       </c>
-      <c r="G9" s="64" t="s">
+      <c r="G9" s="53" t="s">
         <v>498</v>
       </c>
     </row>
@@ -5420,632 +5451,634 @@
     <mergeCell ref="B2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="B2:N28"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="13" width="12" customWidth="1"/>
+    <col min="5" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="17.7109375" customWidth="1"/>
+    <col min="9" max="13" width="12" customWidth="1"/>
     <col min="14" max="14" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="36" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="66" t="s">
+    <row r="2" spans="2:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="80" t="s">
         <v>509</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="67" t="s">
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+      <c r="L2" s="80"/>
+      <c r="M2" s="80"/>
+      <c r="N2" s="80"/>
+    </row>
+    <row r="4" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="81" t="s">
         <v>510</v>
       </c>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-    </row>
-    <row r="5" ht="22" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="81"/>
+      <c r="M4" s="81"/>
+      <c r="N4" s="81"/>
+    </row>
+    <row r="5" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="11" t="s">
         <v>511</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="77" t="s">
         <v>512</v>
       </c>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-    </row>
-    <row r="6" ht="22" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B6" s="24" t="s">
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
+      <c r="N5" s="77"/>
+    </row>
+    <row r="6" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="18" t="s">
         <v>513</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="76" t="s">
         <v>514</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" ht="22" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
+      <c r="D6" s="76"/>
+      <c r="E6" s="76"/>
+      <c r="F6" s="76"/>
+      <c r="G6" s="76"/>
+      <c r="H6" s="76"/>
+      <c r="I6" s="76"/>
+      <c r="J6" s="76"/>
+      <c r="K6" s="76"/>
+      <c r="L6" s="76"/>
+      <c r="M6" s="76"/>
+      <c r="N6" s="76"/>
+    </row>
+    <row r="7" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="11" t="s">
         <v>515</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C7" s="77" t="s">
         <v>516</v>
       </c>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-    </row>
-    <row r="8" ht="22" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B8" s="24" t="s">
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="77"/>
+      <c r="M7" s="77"/>
+      <c r="N7" s="77"/>
+    </row>
+    <row r="8" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="18" t="s">
         <v>517</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="76" t="s">
         <v>518</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" ht="22" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="14" t="s">
+      <c r="D8" s="76"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="76"/>
+      <c r="J8" s="76"/>
+      <c r="K8" s="76"/>
+      <c r="L8" s="76"/>
+      <c r="M8" s="76"/>
+      <c r="N8" s="76"/>
+    </row>
+    <row r="9" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="11" t="s">
         <v>519</v>
       </c>
-      <c r="C9" s="43" t="s">
+      <c r="C9" s="77" t="s">
         <v>520</v>
       </c>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="24" t="s">
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="77"/>
+      <c r="K9" s="77"/>
+      <c r="L9" s="77"/>
+      <c r="M9" s="77"/>
+      <c r="N9" s="77"/>
+    </row>
+    <row r="10" spans="2:14" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="18" t="s">
         <v>521</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="76" t="s">
         <v>522</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B12" s="68" t="s">
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="76"/>
+      <c r="K10" s="76"/>
+      <c r="L10" s="76"/>
+      <c r="M10" s="76"/>
+      <c r="N10" s="76"/>
+    </row>
+    <row r="12" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="78" t="s">
         <v>523</v>
       </c>
-      <c r="C12" s="68"/>
-      <c r="D12" s="68"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="68"/>
-      <c r="K12" s="68"/>
-      <c r="L12" s="68"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="68"/>
-    </row>
-    <row r="13" ht="40" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="69" t="s">
+      <c r="C12" s="78"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="78"/>
+      <c r="G12" s="78"/>
+      <c r="H12" s="78"/>
+      <c r="I12" s="78"/>
+      <c r="J12" s="78"/>
+      <c r="K12" s="78"/>
+      <c r="L12" s="78"/>
+      <c r="M12" s="78"/>
+      <c r="N12" s="78"/>
+    </row>
+    <row r="13" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="55" t="s">
         <v>524</v>
       </c>
-      <c r="D13" s="69" t="s">
+      <c r="D13" s="55" t="s">
         <v>525</v>
       </c>
-      <c r="E13" s="69" t="s">
+      <c r="E13" s="55" t="s">
         <v>526</v>
       </c>
-      <c r="F13" s="69" t="s">
+      <c r="F13" s="55" t="s">
         <v>527</v>
       </c>
-      <c r="G13" s="69" t="s">
+      <c r="G13" s="55" t="s">
         <v>528</v>
       </c>
-      <c r="H13" s="69" t="s">
+      <c r="H13" s="55" t="s">
         <v>529</v>
       </c>
-      <c r="I13" s="69" t="s">
+      <c r="I13" s="55" t="s">
         <v>530</v>
       </c>
-      <c r="J13" s="69" t="s">
+      <c r="J13" s="55" t="s">
         <v>531</v>
       </c>
-      <c r="K13" s="69" t="s">
+      <c r="K13" s="55" t="s">
         <v>532</v>
       </c>
-      <c r="L13" s="69" t="s">
+      <c r="L13" s="55" t="s">
         <v>533</v>
       </c>
-      <c r="M13" s="69" t="s">
+      <c r="M13" s="55" t="s">
         <v>534</v>
       </c>
-      <c r="N13" s="69" t="s">
+      <c r="N13" s="55" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="14" ht="40" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="19" t="s">
+    <row r="14" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="15" t="s">
         <v>536</v>
       </c>
-      <c r="C14" s="70" t="s">
+      <c r="C14" s="56" t="s">
         <v>537</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E14" s="71" t="s">
+      <c r="E14" s="57" t="s">
         <v>539</v>
       </c>
-      <c r="F14" s="72">
+      <c r="F14" s="58">
         <v>8</v>
       </c>
-      <c r="G14" s="72">
+      <c r="G14" s="58">
         <v>9.5</v>
       </c>
-      <c r="H14" s="72">
+      <c r="H14" s="58">
         <v>8.5</v>
       </c>
-      <c r="I14" s="72">
+      <c r="I14" s="58">
         <v>9</v>
       </c>
-      <c r="J14" s="71" t="s">
+      <c r="J14" s="57" t="s">
         <v>540</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K14" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="L14" s="71" t="s">
+      <c r="L14" s="57" t="s">
         <v>542</v>
       </c>
-      <c r="M14" s="71" t="s">
+      <c r="M14" s="57" t="s">
         <v>543</v>
       </c>
-      <c r="N14" s="73" t="s">
+      <c r="N14" s="59" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="15" ht="40" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="21" t="s">
+    <row r="15" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="17" t="s">
         <v>545</v>
       </c>
-      <c r="C15" s="74" t="s">
+      <c r="C15" s="60" t="s">
         <v>546</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="8" t="s">
         <v>547</v>
       </c>
-      <c r="E15" s="71" t="s">
+      <c r="E15" s="57" t="s">
         <v>539</v>
       </c>
-      <c r="F15" s="72">
+      <c r="F15" s="58">
         <v>8.5</v>
       </c>
-      <c r="G15" s="72">
+      <c r="G15" s="58">
         <v>9</v>
       </c>
-      <c r="H15" s="72">
+      <c r="H15" s="58">
         <v>9</v>
       </c>
-      <c r="I15" s="72">
+      <c r="I15" s="58">
         <v>9.5</v>
       </c>
-      <c r="J15" s="71" t="s">
+      <c r="J15" s="57" t="s">
         <v>548</v>
       </c>
-      <c r="K15" s="10" t="s">
+      <c r="K15" s="7" t="s">
         <v>549</v>
       </c>
-      <c r="L15" s="71" t="s">
+      <c r="L15" s="57" t="s">
         <v>542</v>
       </c>
-      <c r="M15" s="71" t="s">
+      <c r="M15" s="57" t="s">
         <v>543</v>
       </c>
-      <c r="N15" s="73" t="s">
+      <c r="N15" s="59" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="16" ht="40" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B16" s="19" t="s">
+    <row r="16" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="15" t="s">
         <v>551</v>
       </c>
-      <c r="C16" s="70" t="s">
+      <c r="C16" s="56" t="s">
         <v>552</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="E16" s="71" t="s">
+      <c r="E16" s="57" t="s">
         <v>539</v>
       </c>
-      <c r="F16" s="72">
+      <c r="F16" s="58">
         <v>8</v>
       </c>
-      <c r="G16" s="72">
+      <c r="G16" s="58">
         <v>8.5</v>
       </c>
-      <c r="H16" s="72">
+      <c r="H16" s="58">
         <v>8</v>
       </c>
-      <c r="I16" s="72">
+      <c r="I16" s="58">
         <v>8.5</v>
       </c>
-      <c r="J16" s="71" t="s">
+      <c r="J16" s="57" t="s">
         <v>554</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="L16" s="71" t="s">
+      <c r="L16" s="57" t="s">
         <v>556</v>
       </c>
-      <c r="M16" s="75" t="s">
+      <c r="M16" s="61" t="s">
         <v>557</v>
       </c>
-      <c r="N16" s="73" t="s">
+      <c r="N16" s="59" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="17" ht="40" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B17" s="21" t="s">
+    <row r="17" spans="2:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="17" t="s">
         <v>559</v>
       </c>
-      <c r="C17" s="74" t="s">
+      <c r="C17" s="60" t="s">
         <v>560</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="E17" s="71" t="s">
+      <c r="E17" s="57" t="s">
         <v>539</v>
       </c>
-      <c r="F17" s="72">
+      <c r="F17" s="58">
         <v>8.5</v>
       </c>
-      <c r="G17" s="72">
+      <c r="G17" s="58">
         <v>9</v>
       </c>
-      <c r="H17" s="72">
+      <c r="H17" s="58">
         <v>8.5</v>
       </c>
-      <c r="I17" s="72">
+      <c r="I17" s="58">
         <v>8.5</v>
       </c>
-      <c r="J17" s="71" t="s">
+      <c r="J17" s="57" t="s">
         <v>562</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="7" t="s">
         <v>563</v>
       </c>
-      <c r="L17" s="71" t="s">
+      <c r="L17" s="57" t="s">
         <v>556</v>
       </c>
-      <c r="M17" s="75" t="s">
+      <c r="M17" s="61" t="s">
         <v>557</v>
       </c>
-      <c r="N17" s="73" t="s">
+      <c r="N17" s="59" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="76" t="s">
+    <row r="18" spans="2:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="76" t="s">
+      <c r="D18" s="62" t="s">
         <v>565</v>
       </c>
-      <c r="E18" s="76" t="s">
+      <c r="E18" s="62" t="s">
         <v>566</v>
       </c>
-      <c r="F18" s="76" t="s">
+      <c r="F18" s="62" t="s">
         <v>567</v>
       </c>
-      <c r="G18" s="76" t="s">
+      <c r="G18" s="62" t="s">
         <v>568</v>
       </c>
-      <c r="H18" s="76" t="s">
+      <c r="H18" s="62" t="s">
         <v>569</v>
       </c>
-      <c r="I18" s="76" t="s">
+      <c r="I18" s="62" t="s">
         <v>570</v>
       </c>
-      <c r="J18" s="76" t="s">
+      <c r="J18" s="62" t="s">
         <v>571</v>
       </c>
-      <c r="K18" s="76" t="s">
+      <c r="K18" s="62" t="s">
         <v>572</v>
       </c>
-      <c r="L18" s="76" t="s">
+      <c r="L18" s="62" t="s">
         <v>573</v>
       </c>
-      <c r="M18" s="76" t="s">
+      <c r="M18" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="N18" s="76" t="s">
+      <c r="N18" s="62" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="77" t="s">
+    <row r="20" spans="2:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="79" t="s">
         <v>574</v>
       </c>
-      <c r="C20" s="77"/>
-      <c r="D20" s="77"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="77"/>
-      <c r="K20" s="77"/>
-      <c r="L20" s="77"/>
-      <c r="M20" s="77"/>
-      <c r="N20" s="77"/>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B21" s="47" t="s">
+      <c r="C20" s="79"/>
+      <c r="D20" s="79"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="79"/>
+      <c r="G20" s="79"/>
+      <c r="H20" s="79"/>
+      <c r="I20" s="79"/>
+      <c r="J20" s="79"/>
+      <c r="K20" s="79"/>
+      <c r="L20" s="79"/>
+      <c r="M20" s="79"/>
+      <c r="N20" s="79"/>
+    </row>
+    <row r="21" spans="2:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="38" t="s">
         <v>575</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="38" t="s">
         <v>576</v>
       </c>
-      <c r="D21" s="47" t="s">
+      <c r="D21" s="38" t="s">
         <v>577</v>
       </c>
-      <c r="E21" s="47" t="s">
+      <c r="E21" s="38" t="s">
         <v>578</v>
       </c>
-      <c r="F21" s="47" t="s">
+      <c r="F21" s="38" t="s">
         <v>579</v>
       </c>
-      <c r="G21" s="47" t="s">
+      <c r="G21" s="38" t="s">
         <v>580</v>
       </c>
-      <c r="H21" s="47" t="s">
+      <c r="H21" s="38" t="s">
         <v>581</v>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="70" t="s">
+    <row r="22" spans="2:14" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="56" t="s">
         <v>582</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="18" t="s">
         <v>583</v>
       </c>
-      <c r="D22" s="31" t="s">
+      <c r="D22" s="23" t="s">
         <v>584</v>
       </c>
-      <c r="E22" s="71" t="s">
+      <c r="E22" s="57" t="s">
         <v>585</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="15" t="s">
         <v>587</v>
       </c>
-      <c r="H22" s="32" t="s">
+      <c r="H22" s="24" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="78" t="s">
+    <row r="23" spans="2:14" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="63" t="s">
         <v>589</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="19" t="s">
         <v>590</v>
       </c>
-      <c r="D23" s="50" t="s">
+      <c r="D23" s="41" t="s">
         <v>591</v>
       </c>
-      <c r="E23" s="71" t="s">
+      <c r="E23" s="57" t="s">
         <v>585</v>
       </c>
-      <c r="F23" s="51" t="s">
+      <c r="F23" s="42" t="s">
         <v>586</v>
       </c>
-      <c r="G23" s="30" t="s">
+      <c r="G23" s="22" t="s">
         <v>587</v>
       </c>
-      <c r="H23" s="79" t="s">
+      <c r="H23" s="64" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="70" t="s">
+    <row r="24" spans="2:14" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="56" t="s">
         <v>593</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="18" t="s">
         <v>594</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="23" t="s">
         <v>595</v>
       </c>
-      <c r="E24" s="75" t="s">
+      <c r="E24" s="61" t="s">
         <v>596</v>
       </c>
-      <c r="F24" s="8" t="s">
+      <c r="F24" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="15" t="s">
         <v>597</v>
       </c>
-      <c r="H24" s="32" t="s">
+      <c r="H24" s="24" t="s">
         <v>598</v>
       </c>
     </row>
-    <row r="25" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="78" t="s">
+    <row r="25" spans="2:14" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="63" t="s">
         <v>599</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="19" t="s">
         <v>600</v>
       </c>
-      <c r="D25" s="50" t="s">
+      <c r="D25" s="41" t="s">
         <v>601</v>
       </c>
-      <c r="E25" s="75" t="s">
+      <c r="E25" s="61" t="s">
         <v>596</v>
       </c>
-      <c r="F25" s="51" t="s">
+      <c r="F25" s="42" t="s">
         <v>586</v>
       </c>
-      <c r="G25" s="30" t="s">
+      <c r="G25" s="22" t="s">
         <v>597</v>
       </c>
-      <c r="H25" s="79" t="s">
+      <c r="H25" s="64" t="s">
         <v>602</v>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="70" t="s">
+    <row r="26" spans="2:14" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="56" t="s">
         <v>603</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="18" t="s">
         <v>604</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="D26" s="23" t="s">
         <v>605</v>
       </c>
-      <c r="E26" s="71" t="s">
+      <c r="E26" s="57" t="s">
         <v>585</v>
       </c>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="G26" s="19" t="s">
+      <c r="G26" s="15" t="s">
         <v>587</v>
       </c>
-      <c r="H26" s="32" t="s">
+      <c r="H26" s="24" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="78" t="s">
+    <row r="27" spans="2:14" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="63" t="s">
         <v>607</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C27" s="19" t="s">
         <v>608</v>
       </c>
-      <c r="D27" s="50" t="s">
+      <c r="D27" s="41" t="s">
         <v>609</v>
       </c>
-      <c r="E27" s="75" t="s">
+      <c r="E27" s="61" t="s">
         <v>596</v>
       </c>
-      <c r="F27" s="51" t="s">
+      <c r="F27" s="42" t="s">
         <v>586</v>
       </c>
-      <c r="G27" s="30" t="s">
+      <c r="G27" s="22" t="s">
         <v>597</v>
       </c>
-      <c r="H27" s="79" t="s">
+      <c r="H27" s="64" t="s">
         <v>610</v>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="70" t="s">
+    <row r="28" spans="2:14" ht="69.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="56" t="s">
         <v>611</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="18" t="s">
         <v>612</v>
       </c>
-      <c r="D28" s="31" t="s">
+      <c r="D28" s="23" t="s">
         <v>613</v>
       </c>
-      <c r="E28" s="75" t="s">
+      <c r="E28" s="61" t="s">
         <v>596</v>
       </c>
-      <c r="F28" s="8" t="s">
+      <c r="F28" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="G28" s="19" t="s">
+      <c r="G28" s="15" t="s">
         <v>597</v>
       </c>
-      <c r="H28" s="32" t="s">
+      <c r="H28" s="24" t="s">
         <v>614</v>
       </c>
     </row>
@@ -6063,6 +6096,6 @@
     <mergeCell ref="B20:N20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>